--- a/app/Imports/excel-importation/data-excel-2025-avec-tables-parametrage.xlsx
+++ b/app/Imports/excel-importation/data-excel-2025-avec-tables-parametrage.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.benaya\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Developpement 2025\grace_back_prod\app\Imports\excel-importation\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F85D12-9279-4B1C-9FEE-C519243A8236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="598">
   <si>
     <t>nom</t>
   </si>
@@ -1824,12 +1825,15 @@
   </si>
   <si>
     <t>السجن المحلي بالصويرة 2</t>
+  </si>
+  <si>
+    <t>adresse</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2179,8 +2183,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7" bestFit="1" customWidth="1"/>
@@ -2203,7 +2207,7 @@
     <col min="23" max="23" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>333</v>
       </c>
@@ -2273,8 +2277,11 @@
       <c r="W1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>3</v>
       </c>
@@ -2343,7 +2350,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -2412,7 +2419,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2477,7 +2484,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2546,7 +2553,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -2615,7 +2622,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -2684,7 +2691,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -2753,7 +2760,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -2822,7 +2829,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -2891,7 +2898,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
@@ -2960,7 +2967,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>3</v>
       </c>
@@ -3029,7 +3036,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>3</v>
       </c>
@@ -3098,7 +3105,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>3</v>
       </c>
@@ -3167,7 +3174,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>3</v>
       </c>
@@ -3236,7 +3243,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>3</v>
       </c>
@@ -4118,14 +4125,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:W28"/>
+  <autoFilter ref="B1:W28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4987,7 +4994,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5026,7 +5033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5224,7 +5231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5430,7 +5437,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6406,7 +6413,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
